--- a/Pruebas calificadas/COLEGIO JOSE MANUEL RESTREPO DIAGNOSTICA 703_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO JOSE MANUEL RESTREPO DIAGNOSTICA 703_CALIFICADO.xlsx
@@ -858,9 +858,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -1613,9 +1613,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -1866,9 +1866,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -2119,9 +2119,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -2364,9 +2364,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3123,9 +3123,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3882,9 +3882,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4388,9 +4388,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -4894,9 +4894,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -5147,9 +5147,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -5400,9 +5400,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5906,9 +5906,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -6159,9 +6159,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6412,9 +6412,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -7424,9 +7424,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -7930,9 +7930,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -8183,9 +8183,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -8436,9 +8436,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO JOSE MANUEL RESTREPO DIAGNOSTICA 703_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO JOSE MANUEL RESTREPO DIAGNOSTICA 703_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1562,11 +1550,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -1574,7 +1558,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1815,11 +1799,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -1827,7 +1807,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2068,11 +2048,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -2080,7 +2056,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2313,11 +2289,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -2325,7 +2297,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2566,11 +2538,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -2578,7 +2546,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2819,11 +2787,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -2831,7 +2795,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3072,11 +3036,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -3084,7 +3044,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3325,11 +3285,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -3337,7 +3293,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3578,11 +3534,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -3590,7 +3542,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3831,11 +3783,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -3843,7 +3791,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4084,11 +4032,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -4096,7 +4040,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4337,11 +4281,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -4349,7 +4289,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4590,11 +4530,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -4602,7 +4538,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4843,11 +4779,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -4855,7 +4787,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5096,11 +5028,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -5108,7 +5036,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5349,11 +5277,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -5361,7 +5285,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5602,11 +5526,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -5614,7 +5534,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5855,11 +5775,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -5867,7 +5783,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6108,11 +6024,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -6120,7 +6032,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6361,11 +6273,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -6373,7 +6281,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6614,11 +6522,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -6626,7 +6530,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6867,11 +6771,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -6879,7 +6779,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7120,11 +7020,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -7132,7 +7028,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7373,11 +7269,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -7385,7 +7277,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7626,11 +7518,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -7638,7 +7526,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7879,11 +7767,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -7891,7 +7775,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8132,11 +8016,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -8144,7 +8024,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8385,11 +8265,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -8397,7 +8273,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8638,11 +8514,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -8650,7 +8522,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8891,11 +8763,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -8903,7 +8771,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9140,11 +9008,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -9152,7 +9016,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9393,11 +9257,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -9405,7 +9265,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9646,11 +9506,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -9658,7 +9514,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9899,11 +9755,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -9911,7 +9763,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10152,11 +10004,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -10164,7 +10012,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10405,11 +10253,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -10417,7 +10261,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10658,11 +10502,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -10670,7 +10510,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10911,11 +10751,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -10923,7 +10759,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11164,11 +11000,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -11176,7 +11008,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11417,11 +11249,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -11429,7 +11257,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11670,11 +11498,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -11682,7 +11506,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11923,11 +11747,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -11935,7 +11755,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12164,11 +11984,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -12176,7 +11992,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12417,11 +12233,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -12429,7 +12241,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12670,11 +12482,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -12682,7 +12490,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12923,11 +12731,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -12935,7 +12739,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13176,11 +12980,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -13188,7 +12988,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13429,11 +13229,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -13441,7 +13237,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13682,11 +13478,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -13694,7 +13486,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13935,11 +13727,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -13947,7 +13735,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14188,11 +13976,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -14200,7 +13984,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14405,11 +14189,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -14417,7 +14197,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14610,11 +14390,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -14622,7 +14398,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14815,11 +14591,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -14827,7 +14599,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15068,11 +14840,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -15080,7 +14848,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -15321,11 +15089,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -15333,7 +15097,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15570,11 +15334,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -15582,7 +15342,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -15823,11 +15583,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -15835,7 +15591,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -16076,11 +15832,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001045535</t>
@@ -16088,7 +15840,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MANUEL RESTREPO (IED)</t>
+          <t>COLEGIO JOSE MANUEL RESTREPO</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
